--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:36Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:37Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:54Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:35Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00Z</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:36Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:37Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:38Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00Z</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00Z</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:35Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00Z</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:34Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:55Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:55Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:55Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:55Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:36Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:55Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:39Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:56Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:56Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:56Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:38Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:57Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:57Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:42Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:57Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:57Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:57Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:41Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:58Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:44Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:58Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:58Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:58Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:59Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:59Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:59Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:47Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:59Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:00Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:00Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:00Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:00Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:01Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:49Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:01Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:49Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:01Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:50Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:02Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:50Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:51Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:51Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:02Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:52Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:02Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:53Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:53Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:54Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-31T06:38:54Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-05-31T06:40:26Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-31T06:40:26Z</t>
+          <t>2026-05-31T13:28:31Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,52 +933,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,52 +1025,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,32 +1117,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t>2026-08-31T10:00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,17 +1209,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,22 +1239,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,42 +1301,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,42 +1393,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,42 +1485,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,17 +1577,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,52 +1669,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Reshiram Raid Hour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-03T18:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,37 +1761,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,52 +1853,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,52 +1945,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,42 +2037,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,42 +2129,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2174,22 +2174,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,17 +2221,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,52 +2313,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,67 +2405,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,67 +2497,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,42 +2681,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,17 +2773,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2798,17 +2798,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,37 +2957,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,37 +3049,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,52 +3141,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,42 +3233,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,42 +3325,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,17 +3417,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,52 +3509,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,52 +3601,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,52 +3693,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,37 +3785,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,67 +4061,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,42 +4153,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,42 +4245,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4290,22 +4290,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,67 +4337,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,17 +4521,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,17 +4613,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,67 +4705,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,67 +4797,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,67 +4889,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,67 +4981,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5073,67 +5073,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,67 +5165,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,17 +5257,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,67 +5349,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,22 +5441,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5471,22 +5471,22 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,67 +5533,67 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-31T13:28:31Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,67 +749,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,52 +841,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,52 +933,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,32 +1025,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t>2026-08-31T10:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,42 +1209,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,42 +1301,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,22 +1346,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,42 +1393,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,17 +1485,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Reshiram Raid Hour</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-03T18:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,52 +1669,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,52 +1761,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,52 +1853,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,42 +1945,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,42 +2037,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,52 +2221,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,67 +2313,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,67 +2405,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,67 +2497,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,42 +2589,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2634,22 +2634,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,17 +2681,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,52 +2773,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,37 +2957,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,52 +3049,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,42 +3141,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,42 +3233,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,17 +3325,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3350,17 +3350,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,52 +3417,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,52 +3509,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,52 +3601,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,37 +3693,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,42 +4061,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4106,22 +4106,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,42 +4153,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,67 +4245,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,67 +4337,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,17 +4429,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,17 +4521,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,67 +4613,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,67 +4705,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,67 +4797,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,67 +4889,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,67 +4981,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5073,67 +5073,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,17 +5165,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,67 +5257,67 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,22 +5349,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5379,22 +5379,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-01T17:31:50Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,67 +5441,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5526,49 +5526,49 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,17 +5578,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -197,42 +197,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>ca0647626c7ecd96</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Pokemon Fossil Museum - Chicago</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Pokemon Fossil Museum - Chicago</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-22T09:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2027-04-11T17:00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-fossil-museum-chicago-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -289,42 +289,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ca0647626c7ecd96</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pokemon Fossil Museum - Chicago</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pokemon Fossil Museum - Chicago</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-22T09:00:00</t>
+          <t>2026-05-26T20:00:00Z</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2027-04-11T17:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -334,22 +334,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-fossil-museum-chicago-2026</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,42 +381,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,52 +565,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,52 +657,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31T10:00:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,42 +841,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,52 +1025,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,42 +1117,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,52 +1209,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram Raid Hour</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-03T18:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,67 +1301,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,42 +1485,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,67 +1577,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,52 +1669,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,52 +1761,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,52 +1853,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,42 +1945,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,42 +2129,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2174,22 +2174,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,52 +2221,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,42 +2313,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,67 +2497,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,52 +2589,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,42 +2681,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,67 +2773,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,52 +2957,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,52 +3049,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,42 +3141,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,22 +3233,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3258,27 +3258,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,52 +3325,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,52 +3509,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,67 +3601,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,52 +3693,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,17 +3785,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,52 +3877,52 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,42 +4061,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4106,22 +4106,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,17 +4153,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,17 +4245,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4275,22 +4275,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,17 +4521,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,52 +4613,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,17 +4705,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,67 +4797,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,67 +4889,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,52 +4981,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5073,67 +5073,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,42 +5165,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5240,39 +5240,39 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5282,42 +5282,42 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5332,69 +5332,69 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-01T17:31:50Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,42 +5441,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5486,22 +5486,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5516,59 +5516,59 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>0a31067443f1ebe5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Shadow Cresselia in Shadow Raids</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Shadow Cresselia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-06T00:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5608,17 +5608,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -105,42 +105,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ec90e50a72b3051a</t>
+          <t>ca0647626c7ecd96</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GO Pass: May</t>
+          <t>Pokemon Fossil Museum - Chicago</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GO Pass: May</t>
+          <t>Pokemon Fossil Museum - Chicago</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-05T10:00:00</t>
+          <t>2026-05-22T09:00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2027-04-11T17:00:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -150,7 +150,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-may-2026</t>
+          <t>https://leekduck.com/events/pokemon-fossil-museum-chicago-2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -197,42 +197,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ca0647626c7ecd96</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pokemon Fossil Museum - Chicago</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pokemon Fossil Museum - Chicago</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-22T09:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2027-04-11T17:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -242,22 +242,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-fossil-museum-chicago-2026</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -289,42 +289,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00Z</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -334,22 +334,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,17 +381,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -406,17 +406,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,52 +473,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,32 +565,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t>2026-08-31T10:00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,32 +657,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -692,17 +692,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,42 +749,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,42 +841,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,42 +933,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -978,22 +978,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Reshiram Raid Hour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1040,37 +1040,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T18:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,52 +1117,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,22 +1209,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1234,27 +1234,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,22 +1301,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1326,27 +1326,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,67 +1393,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,42 +1485,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,42 +1577,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1684,37 +1684,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,22 +1853,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1878,27 +1878,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,42 +1945,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,42 +2129,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2174,22 +2174,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2236,37 +2236,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,52 +2313,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,52 +2497,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,42 +2681,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2880,37 +2880,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,42 +2957,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,37 +3049,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,52 +3141,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,67 +3233,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,52 +3325,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,17 +3417,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,52 +3509,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,17 +3601,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3718,27 +3718,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,17 +3785,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,67 +4061,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,17 +4153,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,52 +4245,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,52 +4429,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,17 +4521,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,67 +4613,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,67 +4705,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,67 +4797,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,52 +4889,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,52 +4981,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5066,74 +5066,74 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5148,59 +5148,59 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,17 +5210,17 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5257,42 +5257,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5332,59 +5332,59 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5434,49 +5434,49 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>0a31067443f1ebe5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Shadow Cresselia in Shadow Raids</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Shadow Cresselia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-06T00:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,42 +5533,42 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>ec90e50a72b3051a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>GO Pass: May</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>GO Pass: May</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-05T10:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -180,12 +180,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -197,42 +197,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -242,22 +242,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -289,17 +289,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -314,17 +314,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,52 +381,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,32 +473,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,67 +565,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,42 +657,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,42 +749,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Reshiram Raid Hour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -856,37 +856,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T18:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,52 +933,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1050,27 +1050,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,22 +1117,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1142,27 +1142,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,67 +1209,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,42 +1301,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,42 +1393,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,12 +1485,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1500,37 +1500,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,42 +1577,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,22 +1669,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1694,27 +1694,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,52 +1853,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,42 +1945,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,12 +2037,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2052,37 +2052,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,52 +2129,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,22 +2221,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2246,27 +2246,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,52 +2313,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,67 +2405,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,42 +2497,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,42 +2589,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2634,22 +2634,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,12 +2681,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2696,37 +2696,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,37 +2865,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,52 +2957,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,52 +3141,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,52 +3325,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,17 +3417,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,17 +3601,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,67 +3693,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,17 +3785,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,52 +4061,52 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,17 +4153,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,52 +4245,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,67 +4521,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,67 +4613,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,22 +4705,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4735,22 +4735,22 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,52 +4797,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4882,59 +4882,59 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,84 +4964,84 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5073,42 +5073,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5118,17 +5118,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5165,42 +5165,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5240,59 +5240,59 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -190,24 +190,24 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>f2ab33585a9ea8f8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>Shadow Dialga in Shadow Raids</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>Shadow Dialga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -222,17 +222,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Shadow Raid Battles</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -289,52 +289,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f2ab33585a9ea8f8</t>
+          <t>b29c995031cb3197</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shadow Dialga in Shadow Raids</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shadow Dialga</t>
+          <t>GO Pass: June</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>go-pass</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Pass</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-07T10:00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T10:00:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-dialga-in-shadow-raids-june-2026</t>
+          <t>https://leekduck.com/events/go-pass-june-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,32 +381,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b29c995031cb3197</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GO Pass: June</t>
+          <t>Spark's Caretaking Quest</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>go-pass</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GO Pass</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -416,17 +416,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-07T10:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-03T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-pass-june-2026</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,42 +565,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,17 +657,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,52 +841,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reshiram Raid Hour</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-03T18:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,52 +933,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,67 +1025,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:40:44Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -5165,17 +5165,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5250,49 +5250,49 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,42 +5349,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5394,22 +5394,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,42 +5441,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,90 +5533,182 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>0a31067443f1ebe5</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia in Shadow Raids</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Shadow Raid Battles</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>ec90e50a72b3051a</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>go-pass</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2026-05-05T10:00:00</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Local Time</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>leekduck</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2026-05-31T06:39:03Z</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="M62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>archived</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>2026: Chicago</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t>2026-06-10T01:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,52 +841,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-03T16:40:44Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,42 +1117,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,42 +1209,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,17 +1301,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,67 +1485,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,67 +1577,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,67 +1669,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,17 +1853,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,52 +1945,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,52 +2129,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,52 +2221,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,42 +2313,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,42 +2405,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,17 +2497,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,52 +2589,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,52 +2681,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,52 +2773,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,37 +2865,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,67 +2957,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,67 +3141,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,42 +3233,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,42 +3325,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,17 +3601,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,67 +4061,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,67 +4153,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,67 +4245,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,37 +4521,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,22 +4613,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4720,37 +4720,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,17 +4780,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026: Chicago</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-10T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>for Pokémon GO Fest 2026: Chicago</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,22 +933,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,37 +963,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,17 +2773,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2813,27 +2813,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:41Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,37 +2865,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2950,74 +2950,74 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,67 +3141,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,42 +3233,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,42 +3325,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,17 +3601,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>2026-07-21T20:00:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>2026-07-28T20:00:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-08-04T20:00:00</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>2026-07-28T20:00:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>2026-08-04T20:00:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-08-11T20:00:00</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,67 +4061,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,67 +4153,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,67 +4245,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>2026-08-25T20:00:00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>2026-09-01T20:00:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-09-08T20:00:00</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,37 +4521,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,22 +4613,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4720,37 +4720,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,52 +4797,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,52 +4889,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,67 +4981,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5073,42 +5073,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5118,17 +5118,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5165,42 +5165,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,17 +5257,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5349,42 +5349,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5394,22 +5394,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,42 +5441,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5486,22 +5486,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,42 +5533,42 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5625,90 +5625,182 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>0a31067443f1ebe5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia in Shadow Raids</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Shadow Raid Battles</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>ec90e50a72b3051a</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>go-pass</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2026-05-05T10:00:00</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Local Time</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>leekduck</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2026-05-31T06:39:03Z</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="M63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>archived</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:41Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-05T14:42:02Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-05T14:42:02Z</t>
+          <t>2026-06-06T02:46:49Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-06T02:46:49Z</t>
+          <t>2026-06-06T13:23:55Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-06T13:23:55Z</t>
+          <t>2026-06-07T03:30:34Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-07T03:30:34Z</t>
+          <t>2026-06-07T13:44:56Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-07T13:44:56Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>for Pokémon GO Fest 2026: Chicago</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,42 +381,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spark's Caretaking Quest</t>
+          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00Z</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,42 +565,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,42 +657,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,52 +933,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1008,39 +1008,39 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,67 +1117,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,42 +1209,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,17 +1301,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,67 +1485,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,67 +1669,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Flying Taxi 2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,42 +1853,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,52 +1945,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,22 +2129,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2154,27 +2154,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,17 +2221,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,52 +2313,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2480,69 +2480,69 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,52 +2681,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,52 +2773,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-06-27T03:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,84 +2940,84 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,67 +3141,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,42 +3325,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,67 +3601,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,52 +4061,52 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,67 +4153,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,52 +4245,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4320,69 +4320,69 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4422,74 +4422,74 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,69 +4504,69 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,52 +4613,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,69 +4688,69 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Reshiram in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,69 +4780,69 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,42 +4889,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -386,12 +386,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Great League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,42 +381,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,42 +565,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,42 +657,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,17 +749,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,52 +841,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,67 +1025,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,67 +1117,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,42 +1209,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,17 +1301,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,52 +1485,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,52 +1669,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Flying Taxi 2026</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,42 +1853,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,17 +1945,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,52 +2129,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,67 +2221,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,17 +2313,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2343,37 +2343,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>2026-06-27T17:00:00</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-27T03:00:00</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2383,59 +2383,59 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2480,84 +2480,84 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,67 +2681,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,42 +2865,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,67 +2957,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,67 +3325,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,67 +3601,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,67 +3693,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,17 +3877,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,22 +4153,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4183,22 +4183,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4228,24 +4228,24 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4275,37 +4275,37 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,7 +4337,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4372,32 +4372,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4407,17 +4407,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,52 +4429,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,22 +4521,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4546,27 +4546,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4628,37 +4628,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,59 +4688,59 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-10T02:58:35Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Reshiram in 5-star Raid Battles</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,42 +381,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>ac20539a0bbc09c7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Candela's Quest for Victory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-09T10:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,42 +565,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>04e8bbecda1e4b4c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T00:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T00:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,17 +657,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Zekrom Raid Hour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-10T18:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,67 +1025,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,42 +1117,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,17 +1209,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1234,17 +1234,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,52 +1301,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,52 +1485,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,42 +1669,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,17 +1853,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,52 +1945,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,67 +2129,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2199,17 +2199,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,17 +2221,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2251,37 +2251,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>2026-06-27T17:00:00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-27T03:00:00</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2291,59 +2291,59 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2388,84 +2388,84 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,67 +2497,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,42 +2681,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,67 +2865,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,67 +2957,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,17 +3049,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,67 +3233,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,67 +3325,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,67 +3601,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,67 +3693,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,17 +3785,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,37 +3969,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,22 +4061,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4091,22 +4091,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4183,37 +4183,37 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4223,17 +4223,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,7 +4245,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4280,32 +4280,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,52 +4337,52 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,22 +4429,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4454,27 +4454,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,52 +4521,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-10T02:58:35Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,67 +749,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zekrom Raid Hour</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>2026: Copenhagen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-10T18:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,42 +1025,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,52 +1209,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>51d343428e9b0cba</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T10:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18T10:00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/choose-your-path-fossil-fun-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:56Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,52 +1393,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>09796e7fc411f372</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-18T19:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:44Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,52 +1485,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,42 +1669,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,17 +1853,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,52 +1945,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,67 +2129,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-27T03:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2199,17 +2199,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,52 +2221,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>741de22db4a9e2f9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-25T19:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2291,89 +2291,89 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-11T03:33:46Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,67 +2405,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2480,69 +2480,69 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2589,67 +2589,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>49b3afbbca1ef87a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-06-30T10:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-03T20:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01T10:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/choose-your-path-charged-embers-2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:59Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,42 +2681,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>815c6b81983ae848</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-02T19:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-02</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:48Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,17 +2957,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,42 +3049,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,52 +3233,52 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>09af22be2a26eb2a</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-07-16T19:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t>2026-07-16T20:00:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:50Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,67 +3325,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>36e65d6b6fd2b4b1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-07-23T19:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-23T20:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-23</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:51Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,52 +3601,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>b5a119241d762047</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-07-28T10:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-08-03T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-07-29T10:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/choose-your-path-fairy-trail-2026</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:00Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>3b3ad6d265da1ff1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-07-30T19:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30T20:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-30</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3855,17 +3855,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:33:51Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3999,22 +3999,22 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,22 +4061,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>16e0bfa2bce26a30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4091,22 +4091,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-08-11T10:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-08-17T20:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-08-12T10:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/choose-your-path-venom-and-vines-2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4131,74 +4131,74 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-11T03:34:00Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4223,74 +4223,74 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4320,84 +4320,84 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4412,69 +4412,69 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4504,59 +4504,59 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4566,22 +4566,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,42 +4613,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,67 +4705,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4780,69 +4780,69 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4872,24 +4872,24 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4919,22 +4919,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,22 +4981,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5006,27 +5006,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5056,69 +5056,69 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5143,17 +5143,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,17 +5165,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5195,37 +5195,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,52 +5257,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,52 +5349,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,42 +5441,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5486,22 +5486,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,42 +5533,42 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5625,42 +5625,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5670,22 +5670,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5717,90 +5717,1010 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>b2d19879c3bcaea6</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Memories in Motion</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Memories in Motion</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-06-02T10:00:00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9a979535753142a4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Happening Now</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Happening Now</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Theme Event A</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-06-02T10:00:00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:00:00</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-06-09T02:45:45Z</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-06-09T02:45:45Z</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>f83fe27ad883966d</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Dynamax Inkay during Max Monday</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Max Inkay</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Max Mondays</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Max Mondays</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-06-01T06:00:00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:00:00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:00:00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-06-02T03:35:21Z</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-06-02T03:35:21Z</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1c6b5c3edecef88d</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Community Day Vote for August</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Community Day Vote for August</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>community</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Community Day</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:00:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:00:00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>America/Los_Angeles</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>PDT</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:38:25Z</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:38:25Z</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>712863bca2c380a5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026: Tokyo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026: Tokyo</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pokémon GO Fest</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Theme Main</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-05-29T01:00:00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:00:00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Asia/Tokyo</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:38:25Z</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:38:25Z</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9b4a97d186ea12f2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mega Medicham in Mega Raids</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mega Medicham</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mega Raid Battles</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-05-27T06:00:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-06-03T06:00:00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:41:50Z</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:41:50Z</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2b22c40b564423f9</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tapu Fini in 5-star Raid Battles</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tapu Fini</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>5-Star Raid Battles</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-05-27T00:00:00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:41:50Z</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:41:50Z</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8fb1ef8054092141</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>GO Battle League</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>gbl</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>GO Battle League</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-05-26T20:00:00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-06-02T20:00:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>America/Los_Angeles</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9a923b0d64abf17b</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Blanche's Quest for Knowledge</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Blanche's Quest for Knowledge</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Theme Event A</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-05-26T10:00:00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:00:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-06-02T03:35:21Z</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-06-02T03:35:21Z</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0a31067443f1ebe5</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia in Shadow Raids</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Shadow Raid Battles</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>ec90e50a72b3051a</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>go-pass</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>2026-05-05T10:00:00</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Local Time</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>leekduck</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>archived</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:56Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:44Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:46Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:59Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:48Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:50Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:51Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:00Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-11T03:33:51Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:00Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,67 +749,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>0790235a7e0539b5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Dynamax Roggenrola during Max Monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026: Copenhagen</t>
+          <t>Max Roggenrola</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-15T21:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,67 +841,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>215544bc0943dabb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-15T20:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-14T16:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-17T20:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Europe/Copenhagen</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>CEST</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,52 +2865,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>4df13162e47c2c80</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-04T10:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-06T20:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/10th-anniversary-party</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:37Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,67 +2957,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,42 +3049,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,42 +3141,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,67 +3233,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09af22be2a26eb2a</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zubat Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zubat Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-16T19:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-16T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,52 +3325,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>09af22be2a26eb2a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-16T19:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t>2026-07-16T20:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,67 +3417,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36e65d6b6fd2b4b1</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eevee Spotlight Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eevee Spotlight Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-23T19:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-23T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-23</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,52 +3601,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>b5a119241d762047</t>
+          <t>36e65d6b6fd2b4b1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fairy Trail</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fairy Trail</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-28T10:00:00</t>
+          <t>2026-07-23T19:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-29T10:00:00</t>
+          <t>2026-07-23T20:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-fairy-trail-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-23</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,67 +3693,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>b5a119241d762047</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T10:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-03T20:00:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-29T10:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/choose-your-path-fairy-trail-2026</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3b3ad6d265da1ff1</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bidoof Spotlight Hour</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bidoof Spotlight Hour</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-30T19:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-30T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-30</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3855,17 +3855,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>3b3ad6d265da1ff1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-07-30T19:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30T20:00:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-30</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,22 +4061,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16e0bfa2bce26a30</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Choose Your Path: Venom and Vines</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Choose Your Path: Venom and Vines</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4091,22 +4091,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-11T10:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-17T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-12T10:00:00</t>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-venom-and-vines-2026</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,67 +4153,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>16e0bfa2bce26a30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T10:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-17T20:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-12T10:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/choose-your-path-venom-and-vines-2026</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4223,17 +4223,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,67 +4245,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,67 +4337,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,67 +4521,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,17 +4613,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,67 +4705,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,37 +4797,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,22 +4889,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4919,22 +4919,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,24 +4964,24 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4996,37 +4996,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5056,24 +5056,24 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5088,52 +5088,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5143,17 +5143,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5200,32 +5200,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,52 +5257,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,22 +5349,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5374,27 +5374,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,52 +5441,52 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,17 +5533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5558,17 +5558,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5625,7 +5625,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5640,27 +5640,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5670,22 +5670,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5717,42 +5717,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5762,22 +5762,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5809,44 +5809,44 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2026-06-08T20:00:00</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t/>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5901,52 +5901,52 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5993,67 +5993,67 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6085,42 +6085,42 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6130,17 +6130,17 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6177,42 +6177,42 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6222,22 +6222,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,17 +6269,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6361,42 +6361,42 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6406,22 +6406,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6453,42 +6453,42 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6545,42 +6545,42 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6637,90 +6637,182 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>0a31067443f1ebe5</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia in Shadow Raids</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Shadow Raid Battles</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>ec90e50a72b3051a</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>go-pass</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>2026-05-05T10:00:00</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Local Time</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>leekduck</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>archived</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:37Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-12T14:50:04Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,42 +933,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>d018ce0117696315</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Twitch Drops for 2026 Pokémon North American International Championships</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Twitch Drops for 2026 Pokémon North American International Championships</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-16T02:59:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/naic-2026-timed-research-twitch-drops</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:14Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,42 +1025,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,52 +1209,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51d343428e9b0cba</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fossil Fun</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fossil Fun</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-17T10:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-18T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-fossil-fun-2026</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,52 +1301,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>51d343428e9b0cba</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-17T10:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-18T10:00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/choose-your-path-fossil-fun-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,22 +1393,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09796e7fc411f372</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Swinub Spotlight Hour</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Swinub Spotlight Hour</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1418,27 +1418,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-18T19:00:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-18</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,52 +1485,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>09796e7fc411f372</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-18T19:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-18T19:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-06-18T20:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,52 +1669,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,42 +1761,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,42 +1853,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,17 +1945,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,52 +2037,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2129,52 +2129,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,42 +2221,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>741de22db4a9e2f9</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wingull Spotlight Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wingull Spotlight Hour</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-25</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,67 +2313,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>741de22db4a9e2f9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-25T19:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-27T03:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2435,37 +2435,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2475,59 +2475,59 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2572,69 +2572,69 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49b3afbbca1ef87a</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Choose Your Path: Charged Embers</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Choose Your Path: Charged Embers</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-30T10:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-01T10:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-charged-embers-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,67 +2681,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>49b3afbbca1ef87a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T10:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-03T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01T10:00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/choose-your-path-charged-embers-2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2751,17 +2751,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>815c6b81983ae848</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pidgey Spotlight Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pidgey Spotlight Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-02T19:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-02</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,42 +2865,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4df13162e47c2c80</t>
+          <t>815c6b81983ae848</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10th Anniversary Party</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10th Anniversary Party</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-04T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-06T20:00:00</t>
+          <t>2026-07-02T19:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/10th-anniversary-party</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-02</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,52 +2957,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>4df13162e47c2c80</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-04T10:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-06T20:00:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/10th-anniversary-party</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,42 +3141,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f6927e06fcaa66c0</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026: Global</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-11T10:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-12T19:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3233,42 +3233,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3c1ded4d30f86157</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3325,67 +3325,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09af22be2a26eb2a</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zubat Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zubat Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-16T19:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-16T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3417,52 +3417,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>c10e578f89aff1d0</t>
+          <t>09af22be2a26eb2a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Weekend Event</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-18T10:00:00</t>
+          <t>2026-07-16T19:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-19T10:00:00</t>
+          <t>2026-07-16T20:00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/weekend-event-july-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3509,67 +3509,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c160c4678b8f905a</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-18T20:00:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-19T10:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
+          <t>https://leekduck.com/events/weekend-event-july-2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3601,67 +3601,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36e65d6b6fd2b4b1</t>
+          <t>c160c4678b8f905a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eevee Spotlight Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eevee Spotlight Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-23T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-23T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-23</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3693,52 +3693,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>b5a119241d762047</t>
+          <t>36e65d6b6fd2b4b1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fairy Trail</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fairy Trail</t>
+          <t>Eevee Spotlight Hour</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28T10:00:00</t>
+          <t>2026-07-23T19:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-29T10:00:00</t>
+          <t>2026-07-23T20:00:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-fairy-trail-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-23</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3785,67 +3785,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ed835b6291fd0c10</t>
+          <t>b5a119241d762047</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Great League and Master Premier | Forever Forward</t>
+          <t>Choose Your Path: Fairy Trail</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T10:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-03T20:00:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-29T10:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
+          <t>https://leekduck.com/events/choose-your-path-fairy-trail-2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3855,17 +3855,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3877,67 +3877,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3b3ad6d265da1ff1</t>
+          <t>ed835b6291fd0c10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bidoof Spotlight Hour</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bidoof Spotlight Hour</t>
+          <t>Great League and Master Premier | Forever Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-30T19:00:00</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-30T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-30</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_master-premier</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a2a784b25de5a4a4</t>
+          <t>3b3ad6d265da1ff1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
+          <t>Bidoof Spotlight Hour</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-07-30T19:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30T20:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-30</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4039,17 +4039,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4061,67 +4061,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4dfdd53b61416d32</t>
+          <t>a2a784b25de5a4a4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hatch Day</t>
+          <t>Ultra League and Weather Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-08T11:00:00</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-08T17:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/hatch-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_weather-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4153,22 +4153,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16e0bfa2bce26a30</t>
+          <t>4dfdd53b61416d32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Choose Your Path: Venom and Vines</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Choose Your Path: Venom and Vines</t>
+          <t>Hatch Day</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4183,22 +4183,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-11T10:00:00</t>
+          <t>2026-08-08T11:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-17T20:00:00</t>
+          <t>2026-08-08T17:00:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-12T10:00:00</t>
+          <t>2026-08-08T14:00:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-venom-and-vines-2026</t>
+          <t>https://leekduck.com/events/hatch-day-august-2026</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4223,17 +4223,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4245,67 +4245,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>e8d206feaa00b8f7</t>
+          <t>16e0bfa2bce26a30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
+          <t>Choose Your Path: Venom and Vines</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T10:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-17T20:00:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-12T10:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/choose-your-path-venom-and-vines-2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4337,67 +4337,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>f4ff4ab2d29e239f</t>
+          <t>e8d206feaa00b8f7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>August Community Day</t>
+          <t>Master League and Evolution Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-15T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/august-communityday2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_evolution-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4429,67 +4429,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42dafa5a0278b073</t>
+          <t>f4ff4ab2d29e239f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
+          <t>August Community Day</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-15T14:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-15T17:00:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/august-communityday2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4521,67 +4521,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>47fb0039a0d29d1b</t>
+          <t>42dafa5a0278b073</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Great League and Scroll Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-22T14:00:00</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-22T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-august-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_scroll-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4613,67 +4613,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2566819a3b61d8ed</t>
+          <t>47fb0039a0d29d1b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-22T14:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-22T17:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
+          <t>https://leekduck.com/events/raid-day-august-2026</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4705,17 +4705,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>aa22fe2054ec87c5</t>
+          <t>2566819a3b61d8ed</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4735,14 +4735,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>2026-08-25T20:00:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>2026-09-01T20:00:00</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-09-08T20:00:00</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t/>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4797,67 +4797,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>073014daf06be6ce</t>
+          <t>aa22fe2054ec87c5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Forever Forward</t>
+          <t>Great League, Ultra League, and Master League: Mega Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-08T10:00:00</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-12-07T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-23-forever-forward</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-mega-edition</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4889,37 +4889,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7e05259143c79f3c</t>
+          <t>073014daf06be6ce</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Example Event Template (Auto ToC Demo)</t>
+          <t>Forever Forward</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-12-02T20:00:00</t>
+          <t>2026-09-08T10:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-12-03T20:00:00</t>
+          <t>2026-12-07T10:00:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/example_event</t>
+          <t>https://leekduck.com/events/season-23-forever-forward</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-12T14:50:04Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4981,22 +4981,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20a4923d445059a2</t>
+          <t>7e05259143c79f3c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Example Event Template (Auto ToC Demo)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5011,22 +5011,22 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t>2026-12-02T20:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2027-03-02T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2027-03-03T00:00:00</t>
+          <t>2026-12-03T20:00:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
+          <t>https://leekduck.com/events/example_event</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5056,24 +5056,24 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-13T02:58:33Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>71c7d2e51cb42fe3</t>
+          <t>20a4923d445059a2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5088,37 +5088,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-10T19:00:00</t>
+          <t>2027-03-02T00:00:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2027-03-03T00:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260610</t>
+          <t>https://leekduck.com/events/go-tour-fairy-type-timed-research</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-11T15:53:00Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>02d1ba196d0147d3</t>
+          <t>71c7d2e51cb42fe3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5180,52 +5180,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Twitch Drops</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-08T20:00:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-08T06:59:00</t>
+          <t>2026-06-10T19:00:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
+          <t>https://leekduck.com/events/raidhour20260610</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-06-03T16:41:06Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-08T15:42:10Z</t>
+          <t>2026-06-11T15:53:00Z</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0ee70c432f192bbb</t>
+          <t>02d1ba196d0147d3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Twitch Drops</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-08T01:00:00</t>
+          <t>2026-06-08T06:59:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-06-10T20:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago-twitch-drops</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5327,17 +5327,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-03T16:41:06Z</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-08T03:35:56Z</t>
+          <t>2026-06-08T15:42:10Z</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5349,52 +5349,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5ff154fdb2ddaaaa</t>
+          <t>0ee70c432f192bbb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dynamax Electabuzz during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Max Electabuzz</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-08T06:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-08T01:00:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-06-08T21:00:00</t>
+          <t>2026-06-10T20:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-chicago</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-08T03:35:56Z</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5441,22 +5441,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>75e409abaedd8be0</t>
+          <t>5ff154fdb2ddaaaa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Dynamax Electabuzz during Max Monday</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Max Electabuzz</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5466,27 +5466,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T06:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-03T19:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-06-03T20:00:00</t>
+          <t>2026-06-08T21:00:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260603</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-08</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-04T03:37:40Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5533,52 +5533,52 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>33c8cfdb0cb8900b</t>
+          <t>75e409abaedd8be0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mega Audino in Mega Raids</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mega Audino</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-03T19:00:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-03T20:00:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raidhour20260603</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-10T15:24:42Z</t>
+          <t>2026-06-04T03:37:40Z</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5625,17 +5625,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0a9631cef2bfefce</t>
+          <t>33c8cfdb0cb8900b</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino in Mega Raids</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Mega Audino</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-03T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-09T00:00:00</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/mega-audino-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5717,7 +5717,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>891dfd454cebf0c5</t>
+          <t>0a9631cef2bfefce</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5732,27 +5732,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-03T00:00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T00:00:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5762,22 +5762,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/reshiram-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-06-09T14:41:39Z</t>
+          <t>2026-06-10T15:24:42Z</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5809,42 +5809,42 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>b2d19879c3bcaea6</t>
+          <t>891dfd454cebf0c5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Memories in Motion</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-02T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5854,22 +5854,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-09T14:41:39Z</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5901,44 +5901,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9a979535753142a4</t>
+          <t>b2d19879c3bcaea6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Memories in Motion</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>season</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2026-06-08T20:00:00</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t/>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
+          <t>https://leekduck.com/events/season-22-memories-in-motion</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-06-09T02:45:45Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5993,52 +5993,52 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>f83fe27ad883966d</t>
+          <t>9a979535753142a4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dynamax Inkay during Max Monday</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Max Inkay</t>
+          <t>Happening Now</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-01T06:00:00</t>
+          <t>2026-06-02T10:00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t>2026-06-08T20:00:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-06-01T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
+          <t>https://leekduck.com/events/sparks-caretaking-quest</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-09T02:45:45Z</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6085,67 +6085,67 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1c6b5c3edecef88d</t>
+          <t>f83fe27ad883966d</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Dynamax Inkay during Max Monday</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Community Day Vote for August</t>
+          <t>Max Inkay</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-05-31T01:00:00</t>
+          <t>2026-06-01T06:00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-01T01:00:00</t>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-01T21:00:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-01</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-06-01T03:38:25Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6177,42 +6177,42 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>712863bca2c380a5</t>
+          <t>1c6b5c3edecef88d</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026: Tokyo</t>
+          <t>Community Day Vote for August</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-05-29T01:00:00</t>
+          <t>2026-05-31T01:00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-01T11:00:00</t>
+          <t>2026-06-01T01:00:00</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6222,17 +6222,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
+          <t>https://leekduck.com/events/community-day-voting-august-2026</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6269,42 +6269,42 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9b4a97d186ea12f2</t>
+          <t>712863bca2c380a5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mega Medicham in Mega Raids</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mega Medicham</t>
+          <t>2026: Tokyo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-05-27T06:00:00</t>
+          <t>2026-05-29T01:00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-03T06:00:00</t>
+          <t>2026-06-01T11:00:00</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-tokyo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-06-03T03:41:50Z</t>
+          <t>2026-06-01T03:38:25Z</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6361,17 +6361,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2b22c40b564423f9</t>
+          <t>9b4a97d186ea12f2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tapu Fini in 5-star Raid Battles</t>
+          <t>Mega Medicham in Mega Raids</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tapu Fini</t>
+          <t>Mega Medicham</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6386,17 +6386,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-05-27T00:00:00</t>
+          <t>2026-05-27T06:00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-03T06:00:00</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
+          <t>https://leekduck.com/events/mega-medicham-in-mega-raids-may-june-2026</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6453,42 +6453,42 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8fb1ef8054092141</t>
+          <t>2b22c40b564423f9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
+          <t>Tapu Fini</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-05-26T20:00:00</t>
+          <t>2026-05-27T00:00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-02T20:00:00</t>
+          <t>2026-06-02T00:00:00</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
+          <t>https://leekduck.com/events/tapu-fini-in-5-star-raid-battles-may-june-2026</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-03T03:41:50Z</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6545,42 +6545,42 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9a923b0d64abf17b</t>
+          <t>8fb1ef8054092141</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Blanche's Quest for Knowledge</t>
+          <t>Great League, Ultra League, and Master League | Memories in Motion</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-26T10:00:00</t>
+          <t>2026-05-26T20:00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-01T20:00:00</t>
+          <t>2026-06-02T20:00:00</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6590,22 +6590,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
+          <t>https://leekduck.com/events/gbl-memories-in-motion_great-league_ultra-league_master-league-split-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-06-02T03:35:21Z</t>
+          <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6637,42 +6637,42 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0a31067443f1ebe5</t>
+          <t>9a923b0d64abf17b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shadow Cresselia in Shadow Raids</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shadow Cresselia</t>
+          <t>Blanche's Quest for Knowledge</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shadow Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-05-06T00:00:00</t>
+          <t>2026-05-26T10:00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-02T00:00:00</t>
+          <t>2026-06-01T20:00:00</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+          <t>https://leekduck.com/events/blanches-quest-for-knowledge</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-06-02T16:16:28Z</t>
+          <t>2026-06-02T03:35:21Z</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6729,90 +6729,182 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>0a31067443f1ebe5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia in Shadow Raids</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Shadow Cresselia</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Raid Battles</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>raids</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Shadow Raid Battles</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://leekduck.com/events/shadow-cresselia-in-shadow-raids-may-june-2026</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Local Time</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:39:03Z</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:16:28Z</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>archived</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>ec90e50a72b3051a</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>GO Pass: May</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>go-pass</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>GO Pass</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>2026-05-05T10:00:00</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2026-06-02T10:00:00</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>https://leekduck.com/events/go-pass-may-2026</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Local Time</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>leekduck</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>leekduck</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>2026-06-02T16:16:28Z</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>archived</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:14Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-06-13T13:51:33Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-13T13:51:33Z</t>
+          <t>2026-06-14T03:36:55Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-21T20:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00Z</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00Z</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00Z</t>
+          <t>2026-07-28T20:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T20:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00Z</t>
+          <t>2026-08-11T20:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00Z</t>
+          <t>2026-08-18T20:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00Z</t>
+          <t>2026-08-25T20:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00Z</t>
+          <t>2026-09-01T20:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00Z</t>
+          <t>2026-09-08T20:00:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-14T03:36:55Z</t>
+          <t>2026-06-14T13:54:16Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-14T13:54:16Z</t>
+          <t>2026-06-15T03:50:37Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00</t>
+          <t>2026-06-09T20:00:00Z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00</t>
+          <t>2026-06-16T20:00:00Z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00</t>
+          <t>2026-06-23T20:00:00Z</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00</t>
+          <t>2026-06-30T20:00:00Z</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00</t>
+          <t>2026-07-07T20:00:00Z</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14T20:00:00</t>
+          <t>2026-07-14T20:00:00Z</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00</t>
+          <t>2026-07-21T20:00:00Z</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28T20:00:00</t>
+          <t>2026-07-28T20:00:00Z</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-11T20:00:00</t>
+          <t>2026-08-11T20:00:00Z</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-18T20:00:00</t>
+          <t>2026-08-18T20:00:00Z</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-25T20:00:00</t>
+          <t>2026-08-25T20:00:00Z</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-01T20:00:00</t>
+          <t>2026-09-01T20:00:00Z</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-08T20:00:00</t>
+          <t>2026-09-08T20:00:00Z</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-15T03:50:37Z</t>
+          <t>2026-06-15T17:10:12Z</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -272,12 +272,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -364,12 +364,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -381,42 +381,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ac20539a0bbc09c7</t>
+          <t>7d5e9e75824997bd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Candela's Quest for Victory</t>
+          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-09T10:00:00</t>
+          <t>2026-06-09T20:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/candelas-quest-for-victory</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -473,42 +473,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7d5e9e75824997bd</t>
+          <t>f5e095eed3abdae7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny in Mega Raids</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ultra League and Pokémon North America International Championships 2026 Cup: Great League Edition | Forever Forward</t>
+          <t>Mega Lopunny</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09T20:00:00Z</t>
+          <t>2026-06-10T06:00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_pokemon-north-america-international-championships-2026-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -565,42 +565,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04e8bbecda1e4b4c</t>
+          <t>b96a1779ec68ede3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zekrom in 5-star Raid Battles</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zekrom</t>
+          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-10T00:00:00</t>
+          <t>2026-06-16T20:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-16T00:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/zekrom-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -657,17 +657,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f5e095eed3abdae7</t>
+          <t>a0c9f4336ad1cf86</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mega Lopunny in Mega Raids</t>
+          <t>Necrozma in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mega Lopunny</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-10T06:00:00</t>
+          <t>2026-06-17T00:00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-23T00:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-lopunny-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -749,52 +749,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0790235a7e0539b5</t>
+          <t>cfb5f7e9a8a11480</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dynamax Roggenrola during Max Monday</t>
+          <t>Mega Scizor in Mega Raids</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Roggenrola</t>
+          <t>Mega Scizor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-15T06:00:00</t>
+          <t>2026-06-17T06:00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-15T21:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-15</t>
+          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -841,22 +841,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>215544bc0943dabb</t>
+          <t>51d343428e9b0cba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Happening Now</t>
+          <t>Choose Your Path: Fossil Fun</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pokémon GO Fest</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -866,42 +866,42 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Theme Main</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-15T20:00:00</t>
+          <t>2026-06-17T10:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-14T16:00:00</t>
+          <t>2026-06-21T20:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-17T20:00:00</t>
+          <t>2026-06-18T10:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemon-go-fest-2026-copenhagen</t>
+          <t>https://leekduck.com/events/choose-your-path-fossil-fun-2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Europe/Copenhagen</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CEST</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -933,67 +933,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d018ce0117696315</t>
+          <t>be9b5b8276989843</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Twitch Drops for 2026 Pokémon North American International Championships</t>
+          <t>Necrozma Raid Hour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Twitch Drops for 2026 Pokémon North American International Championships</t>
+          <t>Necrozma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T18:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-16T02:59:00</t>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-17T19:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/naic-2026-timed-research-twitch-drops</t>
+          <t>https://leekduck.com/events/raidhour20260617</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-13T02:58:33Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1025,67 +1025,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b96a1779ec68ede3</t>
+          <t>09796e7fc411f372</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Master League: Mega Edition and Sunshine Cup: Great League Edition | Forever Forward</t>
+          <t>Swinub Spotlight Hour</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16T20:00:00Z</t>
+          <t>2026-06-18T19:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t>2026-06-18T19:00:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18T20:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_master-league-mega-edition_sunshine-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1117,52 +1117,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0c9f4336ad1cf86</t>
+          <t>4e56df671a6baa04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Necrozma in 5-star Raid Battles</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Frigibax Community Day</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00</t>
+          <t>2026-06-20T14:00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-23T00:00:00</t>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-20T17:00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/necrozma-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/june-communityday2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1209,52 +1209,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cfb5f7e9a8a11480</t>
+          <t>251541211140ad47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mega Scizor in Mega Raids</t>
+          <t>Dynamax Hoothoot during Max Monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mega Scizor</t>
+          <t>Max Hoothoot</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-17T06:00:00</t>
+          <t>2026-06-22T06:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-22T21:00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-scizor-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1301,22 +1301,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51d343428e9b0cba</t>
+          <t>3e5bd4d95895340d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fossil Fun</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Choose Your Path: Fossil Fun</t>
+          <t>Flying Taxi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1331,22 +1331,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-17T10:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-21T20:00:00</t>
+          <t>2026-06-29T20:00:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-18T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-fossil-fun-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1393,67 +1393,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>be9b5b8276989843</t>
+          <t>c86ff0d4d9caa215</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Necrozma Raid Hour</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Necrozma</t>
+          <t>Great League, Ultra League, and Master League | Forever Forward</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-17T18:00:00</t>
+          <t>2026-06-23T20:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-17T19:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260617</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1485,52 +1485,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09796e7fc411f372</t>
+          <t>f529e3c6117cbffc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Swinub Spotlight Hour</t>
+          <t>Celesteela and Kartana in 5-star Raid Battles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Swinub Spotlight Hour</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>5-Star Raid Battles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-18T19:00:00</t>
+          <t>2026-06-24T00:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-18T19:00:00</t>
+          <t>2026-06-30T00:00:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-18T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-18</t>
+          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1577,52 +1577,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4e56df671a6baa04</t>
+          <t>b11918fd4d7b20c0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Mega Pidgeot in Mega Raids</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frigibax Community Day</t>
+          <t>Mega Pidgeot</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Battles</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-20T14:00:00</t>
+          <t>2026-06-24T06:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t>2026-07-01T06:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-20T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/june-communityday2026</t>
+          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1669,22 +1669,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>251541211140ad47</t>
+          <t>3004cc9c4aafbd32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dynamax Hoothoot during Max Monday</t>
+          <t>Celesteela and Kartana Raid Hour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Max Hoothoot</t>
+          <t>Celesteela and Kartana</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1694,27 +1694,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Raid Hour</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-22T06:00:00</t>
+          <t>2026-06-24T18:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-22T21:00:00</t>
+          <t>2026-06-24T19:00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-22</t>
+          <t>https://leekduck.com/events/raidhour20260624</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,17 +1761,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3e5bd4d95895340d</t>
+          <t>4628a45d2ecf0d82</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Flying Taxi</t>
+          <t>Flying Taxi: Taken Over</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-06-25T00:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-2026</t>
+          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1853,42 +1853,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>c86ff0d4d9caa215</t>
+          <t>741de22db4a9e2f9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Great League, Ultra League, and Master League | Forever Forward</t>
+          <t>Wingull Spotlight Hour</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-23T20:00:00Z</t>
+          <t/>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-06-25T19:00:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_ultra-league_master-league-split-1</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1945,22 +1945,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f529e3c6117cbffc</t>
+          <t>fedba2269d67a987</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana in 5-star Raid Battles</t>
+          <t>Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Mega Skarmory Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1970,42 +1970,42 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5-Star Raid Battles</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24T00:00:00</t>
+          <t>2026-06-27T00:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00</t>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T03:00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/celesteela-kartana-in-5-star-raid-battles-june-2026</t>
+          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-05T02:59:44Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2037,22 +2037,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b11918fd4d7b20c0</t>
+          <t>ce9142908c1cc958</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mega Pidgeot in Mega Raids</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Pidgeot</t>
+          <t>Mega Raid Day</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raid Battles</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2067,22 +2067,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-24T06:00:00</t>
+          <t>2026-06-27T14:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-01T06:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27T17:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/mega-pidgeot-in-mega-raids-june-2026</t>
+          <t>https://leekduck.com/events/raid-day-june-2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2112,39 +2112,39 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-04T14:51:08Z</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3004cc9c4aafbd32</t>
+          <t>bd4a2625927ea74b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana Raid Hour</t>
+          <t>Dynamax Pidove during Max Monday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Celesteela and Kartana</t>
+          <t>Max Pidove</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2154,27 +2154,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raid Hour</t>
+          <t>Max Mondays</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00</t>
+          <t>2026-06-29T06:00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-24T19:00:00</t>
+          <t>2026-06-29T21:00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raidhour20260624</t>
+          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2221,22 +2221,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4628a45d2ecf0d82</t>
+          <t>49b3afbbca1ef87a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flying Taxi: Taken Over</t>
+          <t>Choose Your Path: Charged Embers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Choose Your Path</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00</t>
+          <t>2026-06-30T10:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-29T20:00:00</t>
+          <t>2026-07-03T20:00:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01T10:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/flying-taxi-taken-over-2026</t>
+          <t>https://leekduck.com/events/choose-your-path-charged-embers-2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2313,42 +2313,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>741de22db4a9e2f9</t>
+          <t>b2f84fc05dffffcf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wingull Spotlight Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wingull Spotlight Hour</t>
+          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-06-25</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2405,67 +2405,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fedba2269d67a987</t>
+          <t>815c6b81983ae848</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Skarmory Super Mega Raid Day</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Skarmory Super Mega Raid Day</t>
+          <t>Pidgey Spotlight Hour</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-27T00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t>2026-07-02T19:00:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-27T03:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/skarmory-super-mega-raid-day-2026</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-06-05T02:59:44Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2497,52 +2497,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ce9142908c1cc958</t>
+          <t>4df13162e47c2c80</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mega Raid Day</t>
+          <t>10th Anniversary Party</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Raid Day</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>raids</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mega Raid Battles</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-27T14:00:00</t>
+          <t>2026-07-04T10:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-06T20:00:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-27T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/raid-day-june-2026</t>
+          <t>https://leekduck.com/events/10th-anniversary-party</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2567,74 +2567,74 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-12T03:33:40Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-04T14:51:08Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bd4a2625927ea74b</t>
+          <t>f03b2c748a8872bb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dynamax Pidove during Max Monday</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Max Pidove</t>
+          <t>July Community Day</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Max Mondays</t>
+          <t>Community Day</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-29T06:00:00</t>
+          <t>2026-07-04T14:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00</t>
+          <t>2026-07-04T17:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/max-mondays-2026-06-29</t>
+          <t>https://leekduck.com/events/july-communityday2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2681,67 +2681,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49b3afbbca1ef87a</t>
+          <t>f2e1753f297d8561</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Choose Your Path: Charged Embers</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Choose Your Path: Charged Embers</t>
+          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Choose Your Path</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-30T10:00:00</t>
+          <t>2026-07-07T20:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-03T20:00:00</t>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-01T10:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/choose-your-path-charged-embers-2026</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_ultra-league_fantasy-cup-ultra-league-edition</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2751,17 +2751,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2773,42 +2773,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>b2f84fc05dffffcf</t>
+          <t>f6927e06fcaa66c0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Great League and Summer Cup: Great League Edition | Forever Forward</t>
+          <t>2026: Global</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Pokémon GO Fest</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Main</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00Z</t>
+          <t>2026-07-11T10:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-12T19:00:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/gbl-forever-forward_great-league_summer-cup-great-league-edition</t>
+          <t>https://leekduck.com/events/pokemon-go-fest-2026-global</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Local Time</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2865,42 +2865,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>815c6b81983ae848</t>
+          <t>3c1ded4d30f86157</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pidgey Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pidgey Spotlight Hour</t>
+          <t>Master League and Retro Cup: Great League Edition | Forever Forward</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>gbl</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pokémon Spotlight Hour</t>
+          <t>GO Battle League</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-14T20:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-02T19:00:00</t>
+          <t>2026-07-21T20:00:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-02</t>
+          <t>https://leekduck.com/events/gbl-forever-forward_master-league_retro-cup-great-league-edition</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-06-11T03:34:01Z</t>
+          <t>2026-05-31T06:39:03Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2957,52 +2957,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4df13162e47c2c80</t>
+          <t>09af22be2a26eb2a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10th Anniversary Party</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10th Anniversary Party</t>
+          <t>Zubat Spotlight Hour</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Theme Event A</t>
+          <t>Pokémon Spotlight Hour</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-04T10:00:00</t>
+          <t>2026-07-16T19:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-06T20:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-16T20:00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/10th-anniversary-party</t>
+          <t>https://leekduck.com/events/pokemonspotlighthour2026-07-16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-06-12T03:33:40Z</t>
+          <t>2026-06-11T03:34:01Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3049,67 +3049,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f03b2c748a8872bb</t>
+          <t>d9dd414f70eb7bdb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Raichu Super Mega Raid Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>July Community Day</t>
+          <t>Mega Raichu Super Mega Raid Day</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Raid Day</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>raids</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Community Day</t>
+          <t>Mega Raid Battles</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-04T14:00:00</t>
+          <t>2026-07-18T00:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-04T17:00:00</t>
+          <t>2026-07-18T03:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://leekduck.com/events/july-communityday2026</t>
+          <t>https://leekduck.com/events/raichu-super-mega-raid-day-2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>America/Los_Angeles</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Local Time</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3119,17 +3119,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-05-31T06:39:03Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:42Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-15T17:10:12Z</t>
+          <t>2026-06-16T03:40:41Z</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3141,67 +3141,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f2e1753f297d8561</t>
+          <t>c10e578f89aff1d0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ultra League and Fantasy Cup: Ultra League Edition | Forever Forward</t>
+          <t>Weekend Event</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>gbl</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GO Battle League</t>
+          <t>Theme Event A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-07T20:00:00Z</t>
+          <t>2026-07-18T10:00:00</t>
         </is>
       